--- a/public/inventory_bulk_upload_template.xlsx
+++ b/public/inventory_bulk_upload_template.xlsx
@@ -1,56 +1,74 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
-    <sheet name="Inventory Upload" sheetId="1" r:id="rId1"/>
-    <sheet name="Instructions" sheetId="2" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventory Upload" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Benchmark Upload" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="7">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+    </font>
+    <font>
+      <color rgb="00C00000"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00833C00"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+        <bgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00833C00"/>
+        <bgColor rgb="00833C00"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -65,14 +83,92 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -151,7 +247,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -186,7 +281,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -221,16 +315,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -352,340 +450,531 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.83203125" customWidth="1"/>
-    <col min="2" max="2" width="18.83203125" customWidth="1"/>
-    <col min="3" max="3" width="20.83203125" customWidth="1"/>
-    <col min="4" max="4" width="18.83203125" customWidth="1"/>
-    <col min="5" max="5" width="24.83203125" customWidth="1"/>
-    <col min="6" max="6" width="18.83203125" customWidth="1"/>
-    <col min="7" max="7" width="18.83203125" customWidth="1"/>
-    <col min="8" max="8" width="18.83203125" customWidth="1"/>
-    <col min="9" max="9" width="18.83203125" customWidth="1"/>
-    <col min="10" max="10" width="25.83203125" customWidth="1"/>
-    <col min="11" max="11" width="24.83203125" customWidth="1"/>
-    <col min="12" max="12" width="20.83203125" customWidth="1"/>
-    <col min="13" max="13" width="18.83203125" customWidth="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Brand</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Device Model</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Sample / HW Type</v>
-      </c>
-      <c r="D1" t="str">
-        <v>HW Stage</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Sample Received Date</v>
-      </c>
-      <c r="F1" t="str">
-        <v>VC ID</v>
-      </c>
-      <c r="G1" t="str">
-        <v>IMEI1</v>
-      </c>
-      <c r="H1" t="str">
-        <v>IMEI2</v>
-      </c>
-      <c r="I1" t="str">
-        <v>Color</v>
-      </c>
-      <c r="J1" t="str">
-        <v>Storage / RAM Variant</v>
-      </c>
-      <c r="K1" t="str">
-        <v>Warehouse / Location</v>
-      </c>
-      <c r="L1" t="str">
-        <v>Inventory Holder</v>
-      </c>
-      <c r="M1" t="str">
-        <v>Remarks</v>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Device Model</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Sample / HW Type</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>HW Stage</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Sample Received Date</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>VC ID</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>IMEI1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>IMEI2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Storage / RAM Variant</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Warehouse / Location</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Inventory Holder</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Assigned To</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>Samsung</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Galaxy S25</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Phone</v>
-      </c>
-      <c r="D2" t="str">
-        <v>DVT</v>
-      </c>
-      <c r="E2" t="str">
-        <v>2025-01-15</v>
-      </c>
-      <c r="F2" t="str">
-        <v>VC-10001</v>
-      </c>
-      <c r="G2" t="str">
-        <v>352000001234567</v>
-      </c>
-      <c r="H2" t="str">
-        <v>352000001234568</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Black</v>
-      </c>
-      <c r="J2" t="str">
-        <v>12GB/256GB</v>
-      </c>
-      <c r="K2" t="str">
-        <v>WH-A</v>
-      </c>
-      <c r="L2" t="str">
-        <v>John Smith</v>
-      </c>
-      <c r="M2" t="str">
-        <v/>
-      </c>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Tecno</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Spark 30</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>PR1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>15-Jan-25</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2565243</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>352000001234567</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>352000001234568</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>8GB/128GB</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>WH-A</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>John Smith</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>Apple</v>
-      </c>
-      <c r="B3" t="str">
-        <v>iPhone 17</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Phone</v>
-      </c>
-      <c r="D3" t="str">
-        <v>EVT</v>
-      </c>
-      <c r="E3" t="str">
-        <v>2025-02-01</v>
-      </c>
-      <c r="F3" t="str">
-        <v>VC-10002</v>
-      </c>
-      <c r="G3" t="str">
-        <v>352000009876543</v>
-      </c>
-      <c r="H3" t="str">
-        <v>352000009876544</v>
-      </c>
-      <c r="I3" t="str">
-        <v>White</v>
-      </c>
-      <c r="J3" t="str">
-        <v>8GB/512GB</v>
-      </c>
-      <c r="K3" t="str">
-        <v>WH-B</v>
-      </c>
-      <c r="L3" t="str">
-        <v>Jane Doe</v>
-      </c>
-      <c r="M3" t="str">
-        <v>Priority sample</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Infinix</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Note 40 Pro</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>PR0-1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>EVT</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>01-Feb-25</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2565273</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>352000009876543</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>352000009876544</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>8GB/256GB</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>WH-B</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Jane Doe</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Priority sample</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>OnePlus</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Nord 5</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Phone</v>
-      </c>
-      <c r="D4" t="str">
-        <v>PVT</v>
-      </c>
-      <c r="E4" t="str">
-        <v>2025-03-10</v>
-      </c>
-      <c r="F4" t="str">
-        <v>VC-10003</v>
-      </c>
-      <c r="G4" t="str">
-        <v>352000005551234</v>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>Green</v>
-      </c>
-      <c r="J4" t="str">
-        <v>8GB/128GB</v>
-      </c>
-      <c r="K4" t="str">
-        <v>WH-A</v>
-      </c>
-      <c r="L4" t="str">
-        <v>Raj Kumar</v>
-      </c>
-      <c r="M4" t="str">
-        <v/>
-      </c>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>itel</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>P55</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>PR2</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PVT</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>10-Mar-25</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>3525282</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>352000005551234</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>6GB/128GB</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>WH-A</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Raj Kumar</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M4"/>
-  </ignoredErrors>
+  <dataValidations count="5">
+    <dataValidation sqref="A2:A5000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Invalid Brand" error="Select: itel, Tecno, Infinix, Oraimo, Villaon" type="list">
+      <formula1>"itel,Tecno,Infinix,Oraimo,Villaon,Other"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C2:C5000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Invalid HW Type" error="Select: PR0 / PR0-1 / PR1 / PR1-1 / PR2 / PIR / MPR" type="list">
+      <formula1>"PR0,PR0-1,PR1,PR1-1,PR2,PIR,MPR"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D2:D5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"EVT,DVT,PVT,MP,Other"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G2:G5000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Invalid IMEI1" error="IMEI1 must be exactly 15 digits" type="textLength" operator="equal">
+      <formula1>15</formula1>
+    </dataValidation>
+    <dataValidation sqref="H2:H5000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid IMEI2" error="IMEI2 must be 15 digits if provided" type="textLength" operator="equal">
+      <formula1>15</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A18"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="80.83203125" customWidth="1"/>
+    <col width="88" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>BULK UPLOAD TEMPLATE — Device Sample Inventory</v>
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>TRANSSION — Device Sample Inventory Upload Template v2</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v/>
-      </c>
+      <c r="A2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>MANDATORY FIELDS (must not be empty):</v>
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>MANDATORY FIELDS (must not be empty):</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>Brand, Device Model, Sample / HW Type, HW Stage, IMEI1, Color, Storage / RAM Variant, Warehouse / Location, Inventory Holder</v>
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Brand | Device Model | Sample/HW Type | HW Stage | IMEI1 | Color | Storage/RAM | Location | Inventory Holder</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v/>
-      </c>
+      <c r="A5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="str">
-        <v>OPTIONAL FIELDS:</v>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>DROPDOWN FIELDS:</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="str">
-        <v>Sample Received Date, VC ID, IMEI2, Remarks</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Brand       — itel | Tecno | Infinix | Oraimo | Villaon | Other</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="str">
-        <v/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>HW Type     — PR0 | PR0-1 | PR1 | PR1-1 | PR2 | PIR | MPR</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="str">
-        <v>HW STAGE values: EVT | DVT | PVT | MP | Other</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>HW Stage    — EVT | DVT | PVT | MP | Other</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="str">
-        <v>IMEI format: 15 digits, e.g. 352000001234567</v>
-      </c>
+      <c r="A10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="str">
-        <v>Date format: YYYY-MM-DD, e.g. 2025-01-15</v>
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>VALIDATION RULES:</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="str">
-        <v/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>IMEI1/2     — Must be exactly 15 digits</t>
+        </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="str">
-        <v>DUPLICATE DETECTION:</v>
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Date Format — DD-MMM-YY  e.g. 15-Jan-25 | 01-Feb-25 | 10-Mar-25</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="str">
-        <v>System blocks records where IMEI1, IMEI2, or VC ID already exists in the database.</v>
-      </c>
+      <c r="A14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="str">
-        <v>Duplicate rows are logged and Admin is notified via email.</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>UPLOAD SUMMARY returned after upload:</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>• Total Uploaded • Successful Entries • Failed Entries • Duplicate Entries • Missing Data Records</v>
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Use the 'Benchmark Upload' tab for competitor/benchmark devices.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A18"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Competitor Brand</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Device Model</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>Received Date</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>Serial Number / IMEI</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="H1" s="7" t="inlineStr">
+        <is>
+          <t>Storage / RAM</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>Warehouse / Location</t>
+        </is>
+      </c>
+      <c r="J1" s="7" t="inlineStr">
+        <is>
+          <t>Custodian</t>
+        </is>
+      </c>
+      <c r="K1" s="7" t="inlineStr">
+        <is>
+          <t>Purpose / Test Type</t>
+        </is>
+      </c>
+      <c r="L1" s="7" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="A2:A5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Samsung,Apple,Xiaomi,Vivo,Oppo,Realme,OnePlus,Motorola,Nokia,Google,Huawei,Other"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C2:C5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Smartphone,Tablet,Wearable,TWS,Feature Phone,Other"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/inventory_bulk_upload_template.xlsx
+++ b/public/inventory_bulk_upload_template.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,18 +45,38 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00137333"/>
+    </font>
+    <font>
+      <color rgb="00137333"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+    </font>
+    <font>
+      <color rgb="001F4E79"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="00833C00"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C00000"/>
+        <bgColor rgb="00C00000"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -83,9 +103,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -93,7 +116,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -467,92 +494,92 @@
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Brand</t>
+          <t>Brand *</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Device Model</t>
+          <t>Device Model *</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Sample / HW Type</t>
+          <t>Sample / HW Type *</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>HW Stage</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+          <t>IMEI1 *</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>IMEI2</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Serial Number</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>VC ID</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Storage / RAM Variant</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Assigned Date *</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>Sample Received Date</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>VC ID</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>IMEI1</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>IMEI2</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Color</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Storage / RAM Variant</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Warehouse / Location</t>
-        </is>
-      </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Inventory Holder</t>
+          <t>Warehouse / Location *</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>Inventory Holder *</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
           <t>Assigned To</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
@@ -576,50 +603,54 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>DVT</t>
+          <t>352000001234567</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>352000001234568</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SN001</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2565243</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>8GB/128GB</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>15-Jan-25</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2565243</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>352000001234567</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>352000001234568</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>8GB/128GB</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>10-Jan-25</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>WH-A</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>John Smith</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
     </row>
@@ -641,54 +672,58 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EVT</t>
+          <t>352000009876543</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>352000009876544</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2565273</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>8GB/256GB</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>01-Feb-25</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2565273</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>352000009876543</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>352000009876544</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>8GB/256GB</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>28-Jan-25</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>WH-B</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Jane Doe</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Raj Kumar</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Priority sample</t>
+          <t>Priority</t>
         </is>
       </c>
     </row>
@@ -710,64 +745,61 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PVT</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+          <t>352000005551234</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>SN003</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>6GB/128GB</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>10-Mar-25</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>3525282</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>352000005551234</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Green</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>6GB/128GB</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>05-Mar-25</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>WH-A</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Raj Kumar</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
     </row>
   </sheetData>
-  <dataValidations count="5">
-    <dataValidation sqref="A2:A5000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Invalid Brand" error="Select: itel, Tecno, Infinix, Oraimo, Villaon" type="list">
+  <dataValidations count="4">
+    <dataValidation sqref="A2:A10000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Invalid Brand" error="Select: itel, Tecno, Infinix, Oraimo, Villaon" type="list">
       <formula1>"itel,Tecno,Infinix,Oraimo,Villaon,Other"</formula1>
     </dataValidation>
-    <dataValidation sqref="C2:C5000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Invalid HW Type" error="Select: PR0 / PR0-1 / PR1 / PR1-1 / PR2 / PIR / MPR" type="list">
+    <dataValidation sqref="C2:C10000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Invalid HW Type" error="Select: PR0 / PR0-1 / PR1 / PR1-1 / PR2 / PIR / MPR" type="list">
       <formula1>"PR0,PR0-1,PR1,PR1-1,PR2,PIR,MPR"</formula1>
     </dataValidation>
-    <dataValidation sqref="D2:D5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"EVT,DVT,PVT,MP,Other"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G2:G5000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Invalid IMEI1" error="IMEI1 must be exactly 15 digits" type="textLength" operator="equal">
+    <dataValidation sqref="D2:D10000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Invalid IMEI1" error="IMEI1 must be exactly 15 digits" type="textLength" operator="equal">
       <formula1>15</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H5000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid IMEI2" error="IMEI2 must be 15 digits if provided" type="textLength" operator="equal">
+    <dataValidation sqref="E2:E10000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid IMEI2" error="IMEI2 must be 15 digits if provided" type="textLength" operator="equal">
       <formula1>15</formula1>
     </dataValidation>
   </dataValidations>
@@ -781,16 +813,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="88" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>TRANSSION — Device Sample Inventory Upload Template v2</t>
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>TRANSSION — Device Sample Inventory Upload Template v3</t>
         </is>
       </c>
     </row>
@@ -798,16 +830,16 @@
       <c r="A2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>MANDATORY FIELDS (must not be empty):</t>
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>MANDATORY FIELDS (red header — must not be empty):</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Brand | Device Model | Sample/HW Type | HW Stage | IMEI1 | Color | Storage/RAM | Location | Inventory Holder</t>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Brand | Device Model | Sample/HW Type | IMEI1 | Assigned Date | Warehouse/Location | Inventory Holder</t>
         </is>
       </c>
     </row>
@@ -815,62 +847,103 @@
       <c r="A5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>OPTIONAL FIELDS:</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>IMEI2 | Serial Number | VC ID | Color | Storage/RAM | Sample Received Date | Assigned To | Remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>DROPDOWN FIELDS:</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Brand       — itel | Tecno | Infinix | Oraimo | Villaon | Other</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>HW Type     — PR0 | PR0-1 | PR1 | PR1-1 | PR2 | PIR | MPR</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>HW Stage    — EVT | DVT | PVT | MP | Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>VALIDATION RULES:</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>IMEI1/2     — Must be exactly 15 digits</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Date Format — DD-MMM-YY  e.g. 15-Jan-25 | 01-Feb-25 | 10-Mar-25</t>
-        </is>
-      </c>
-    </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>IMEI1       — Mandatory, exactly 15 digits</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>IMEI2       — Optional, must be 15 digits IF provided</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Date Format — DD-MMM-YY  e.g. 15-Jan-25 | 01-Feb-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>PERFORMANCE NOTE:</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>This template supports 3000+ rows. System validates ALL rows first (fast), then inserts in batches.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>Duplicate detection is done via a single bulk database read — no per-row queries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>Use the 'Benchmark Upload' tab for competitor/benchmark devices.</t>
         </is>
@@ -905,62 +978,62 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>Competitor Brand</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="12" t="inlineStr">
         <is>
           <t>Device Model</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="12" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="12" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="12" t="inlineStr">
         <is>
           <t>Received Date</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="12" t="inlineStr">
         <is>
           <t>Serial Number / IMEI</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="G1" s="12" t="inlineStr">
         <is>
           <t>Color</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="H1" s="12" t="inlineStr">
         <is>
           <t>Storage / RAM</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="I1" s="12" t="inlineStr">
         <is>
           <t>Warehouse / Location</t>
         </is>
       </c>
-      <c r="J1" s="7" t="inlineStr">
+      <c r="J1" s="12" t="inlineStr">
         <is>
           <t>Custodian</t>
         </is>
       </c>
-      <c r="K1" s="7" t="inlineStr">
+      <c r="K1" s="12" t="inlineStr">
         <is>
           <t>Purpose / Test Type</t>
         </is>
       </c>
-      <c r="L1" s="7" t="inlineStr">
+      <c r="L1" s="12" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
